--- a/Output/Tables/Table_div10_adjusted_malf_card.xlsx
+++ b/Output/Tables/Table_div10_adjusted_malf_card.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uccl0-my.sharepoint.com/personal/estela_blanco_uc_cl/Documents/Contaminación_Malformaciones Congénitas/LUR_DLNM/Output/Tables/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uccl0-my.sharepoint.com/personal/estela_blanco_uc_cl/Documents/Contaminación_Malformaciones Congénitas/Pollution_Malformation_TEM/Output/Tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_3041060429E53886CC174040A3FC1950797E0431" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F645D9D-8B5B-0748-8868-584158696FAE}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_1C5D6606B32DF0F8D6F55B0F7FBE1A50797EB43D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B278ED8E-464F-4B4B-ADCC-B4443F65DFD1}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 2" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="84">
   <si>
     <t>Section</t>
   </si>
@@ -58,37 +58,37 @@
     <t>Trimester 1</t>
   </si>
   <si>
-    <t>0.97 (0.81, 1.16)</t>
-  </si>
-  <si>
-    <t>0.82 (0.26, 2.56)</t>
-  </si>
-  <si>
-    <t>0.86 (0.31, 2.40)</t>
+    <t>0.98 (0.81, 1.17)</t>
+  </si>
+  <si>
+    <t>0.87 (0.28, 2.72)</t>
+  </si>
+  <si>
+    <t>0.88 (0.31, 2.47)</t>
   </si>
   <si>
     <t>Trimester 2</t>
   </si>
   <si>
-    <t>1.01 (0.84, 1.21)</t>
-  </si>
-  <si>
-    <t>0.98 (0.31, 3.13)</t>
-  </si>
-  <si>
-    <t>0.91 (0.32, 2.58)</t>
+    <t>1.08 (0.90, 1.30)</t>
+  </si>
+  <si>
+    <t>1.48 (0.47, 4.69)</t>
+  </si>
+  <si>
+    <t>1.44 (0.50, 4.13)</t>
   </si>
   <si>
     <t>Trimester 3</t>
   </si>
   <si>
-    <t>1.21 (1.02, 1.44)</t>
-  </si>
-  <si>
-    <t>3.04 (1.01, 9.15)</t>
-  </si>
-  <si>
-    <t>3.15 (1.17, 8.44)</t>
+    <t>1.12 (0.94, 1.33)</t>
+  </si>
+  <si>
+    <t>1.91 (0.64, 5.64)</t>
+  </si>
+  <si>
+    <t>1.94 (0.73, 5.16)</t>
   </si>
   <si>
     <t>Land-use regression (sp)</t>
@@ -106,151 +106,154 @@
     <t>0.97 (0.90, 1.06)</t>
   </si>
   <si>
-    <t>0.96 (0.36, 2.55)</t>
+    <t>0.99 (0.37, 2.64)</t>
   </si>
   <si>
     <t>0.86 (0.47, 1.55)</t>
   </si>
   <si>
-    <t>0.90 (0.33, 2.43)</t>
-  </si>
-  <si>
-    <t>0.77 (0.43, 1.40)</t>
-  </si>
-  <si>
-    <t>1.03 (0.95, 1.10)</t>
-  </si>
-  <si>
-    <t>1.99 (0.79, 5.03)</t>
-  </si>
-  <si>
-    <t>1.33 (0.79, 2.25)</t>
-  </si>
-  <si>
-    <t>1.18 (0.94, 1.49)</t>
-  </si>
-  <si>
-    <t>2.62 (0.59, 11.53)</t>
-  </si>
-  <si>
-    <t>2.60 (0.72, 9.41)</t>
-  </si>
-  <si>
-    <t>1.00 (0.83, 1.20)</t>
-  </si>
-  <si>
-    <t>0.87 (0.27, 2.78)</t>
-  </si>
-  <si>
-    <t>0.88 (0.31, 2.48)</t>
-  </si>
-  <si>
-    <t>1.35 (1.07, 1.69)</t>
-  </si>
-  <si>
-    <t>5.54 (1.32, 23.28)</t>
-  </si>
-  <si>
-    <t>5.50 (1.59, 19.02)</t>
-  </si>
-  <si>
-    <t>0.99 (0.91, 1.09)</t>
-  </si>
-  <si>
-    <t>1.66 (0.52, 5.31)</t>
-  </si>
-  <si>
-    <t>1.07 (0.56, 2.06)</t>
-  </si>
-  <si>
-    <t>0.96 (0.87, 1.06)</t>
-  </si>
-  <si>
-    <t>0.68 (0.24, 1.97)</t>
-  </si>
-  <si>
-    <t>0.67 (0.35, 1.31)</t>
-  </si>
-  <si>
-    <t>1.04 (0.96, 1.13)</t>
-  </si>
-  <si>
-    <t>2.63 (0.89, 7.78)</t>
-  </si>
-  <si>
-    <t>1.50 (0.84, 2.67)</t>
-  </si>
-  <si>
-    <t>0.93 (0.68, 1.27)</t>
-  </si>
-  <si>
-    <t>0.34 (0.04, 2.57)</t>
-  </si>
-  <si>
-    <t>0.40 (0.07, 2.38)</t>
-  </si>
-  <si>
-    <t>1.17 (0.92, 1.49)</t>
-  </si>
-  <si>
-    <t>1.96 (0.40, 9.49)</t>
-  </si>
-  <si>
-    <t>2.06 (0.53, 8.05)</t>
-  </si>
-  <si>
-    <t>0.95 (0.72, 1.25)</t>
-  </si>
-  <si>
-    <t>0.43 (0.07, 2.47)</t>
-  </si>
-  <si>
-    <t>0.48 (0.10, 2.27)</t>
-  </si>
-  <si>
-    <t>1.30 (0.98, 1.72)</t>
-  </si>
-  <si>
-    <t>3.04 (0.48, 19.12)</t>
-  </si>
-  <si>
-    <t>3.37 (0.70, 16.30)</t>
-  </si>
-  <si>
-    <t>0.89 (0.80, 0.99)</t>
-  </si>
-  <si>
-    <t>0.41 (0.12, 1.34)</t>
-  </si>
-  <si>
-    <t>0.42 (0.21, 0.86)</t>
-  </si>
-  <si>
-    <t>1.07 (0.96, 1.20)</t>
-  </si>
-  <si>
-    <t>2.18 (0.65, 7.28)</t>
-  </si>
-  <si>
-    <t>1.64 (0.78, 3.44)</t>
-  </si>
-  <si>
-    <t>0.91 (0.81, 1.02)</t>
-  </si>
-  <si>
-    <t>0.41 (0.12, 1.45)</t>
-  </si>
-  <si>
-    <t>0.45 (0.21, 0.95)</t>
-  </si>
-  <si>
-    <t>1.08 (0.99, 1.19)</t>
-  </si>
-  <si>
-    <t>2.66 (0.90, 7.92)</t>
-  </si>
-  <si>
-    <t>1.80 (0.98, 3.31)</t>
+    <t>0.99 (0.92, 1.08)</t>
+  </si>
+  <si>
+    <t>1.23 (0.46, 3.27)</t>
+  </si>
+  <si>
+    <t>0.94 (0.52, 1.69)</t>
+  </si>
+  <si>
+    <t>1.00 (0.93, 1.08)</t>
+  </si>
+  <si>
+    <t>1.47 (0.58, 3.75)</t>
+  </si>
+  <si>
+    <t>1.14 (0.65, 1.97)</t>
+  </si>
+  <si>
+    <t>1.15 (0.88, 1.50)</t>
+  </si>
+  <si>
+    <t>2.34 (0.42, 12.92)</t>
+  </si>
+  <si>
+    <t>2.25 (0.51, 10.02)</t>
+  </si>
+  <si>
+    <t>1.12 (0.92, 1.37)</t>
+  </si>
+  <si>
+    <t>1.88 (0.56, 6.33)</t>
+  </si>
+  <si>
+    <t>1.80 (0.59, 5.47)</t>
+  </si>
+  <si>
+    <t>1.25 (0.96, 1.63)</t>
+  </si>
+  <si>
+    <t>3.75 (0.71, 19.90)</t>
+  </si>
+  <si>
+    <t>3.63 (0.85, 15.54)</t>
+  </si>
+  <si>
+    <t>0.97 (0.89, 1.06)</t>
+  </si>
+  <si>
+    <t>1.23 (0.39, 3.92)</t>
+  </si>
+  <si>
+    <t>0.88 (0.46, 1.68)</t>
+  </si>
+  <si>
+    <t>1.01 (0.92, 1.10)</t>
+  </si>
+  <si>
+    <t>1.20 (0.44, 3.24)</t>
+  </si>
+  <si>
+    <t>0.96 (0.51, 1.79)</t>
+  </si>
+  <si>
+    <t>1.00 (0.92, 1.09)</t>
+  </si>
+  <si>
+    <t>1.62 (0.54, 4.92)</t>
+  </si>
+  <si>
+    <t>1.11 (0.61, 2.03)</t>
+  </si>
+  <si>
+    <t>0.87 (0.63, 1.19)</t>
+  </si>
+  <si>
+    <t>0.24 (0.03, 1.90)</t>
+  </si>
+  <si>
+    <t>0.27 (0.05, 1.66)</t>
+  </si>
+  <si>
+    <t>1.11 (0.84, 1.46)</t>
+  </si>
+  <si>
+    <t>1.44 (0.23, 9.17)</t>
+  </si>
+  <si>
+    <t>1.48 (0.30, 7.35)</t>
+  </si>
+  <si>
+    <t>0.99 (0.71, 1.39)</t>
+  </si>
+  <si>
+    <t>0.55 (0.06, 4.72)</t>
+  </si>
+  <si>
+    <t>0.60 (0.09, 3.94)</t>
+  </si>
+  <si>
+    <t>1.20 (0.90, 1.58)</t>
+  </si>
+  <si>
+    <t>2.18 (0.34, 13.99)</t>
+  </si>
+  <si>
+    <t>2.26 (0.45, 11.26)</t>
+  </si>
+  <si>
+    <t>0.90 (0.80, 1.02)</t>
+  </si>
+  <si>
+    <t>0.39 (0.11, 1.44)</t>
+  </si>
+  <si>
+    <t>0.42 (0.19, 0.94)</t>
+  </si>
+  <si>
+    <t>1.04 (0.92, 1.16)</t>
+  </si>
+  <si>
+    <t>1.71 (0.50, 5.86)</t>
+  </si>
+  <si>
+    <t>1.38 (0.65, 2.94)</t>
+  </si>
+  <si>
+    <t>0.95 (0.85, 1.07)</t>
+  </si>
+  <si>
+    <t>0.68 (0.19, 2.42)</t>
+  </si>
+  <si>
+    <t>0.61 (0.29, 1.31)</t>
+  </si>
+  <si>
+    <t>1.06 (0.95, 1.18)</t>
+  </si>
+  <si>
+    <t>2.15 (0.67, 6.95)</t>
+  </si>
+  <si>
+    <t>1.65 (0.82, 3.33)</t>
   </si>
   <si>
     <t>Sheet</t>
@@ -754,13 +757,13 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -771,13 +774,13 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -821,13 +824,13 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -838,13 +841,13 @@
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -855,13 +858,13 @@
         <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -872,13 +875,13 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -889,13 +892,13 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -906,13 +909,13 @@
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -925,7 +928,6 @@
   <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="14.83203125" bestFit="1" customWidth="1"/>
@@ -956,13 +958,13 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -973,13 +975,13 @@
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -990,13 +992,13 @@
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -1007,13 +1009,13 @@
         <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -1024,13 +1026,13 @@
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -1041,13 +1043,13 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -1058,13 +1060,13 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -1075,13 +1077,13 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1096,34 +1098,34 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" t="s">
         <v>82</v>
-      </c>
-      <c r="B4" t="s">
-        <v>81</v>
       </c>
     </row>
   </sheetData>
